--- a/Design-Files/Electrode-Board-v4.0/EMG-Arm-ELEC-v1.0/Deliverables/BOM/JLCPCB-BOM-v1.0.xlsx
+++ b/Design-Files/Electrode-Board-v4.0/EMG-Arm-ELEC-v1.0/Deliverables/BOM/JLCPCB-BOM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="80">
   <si>
     <t>Comment</t>
   </si>
@@ -54,15 +54,12 @@
     <t>MM3Z3V3B</t>
   </si>
   <si>
-    <t>EMG Electrode</t>
+    <t>SEMG PAD</t>
   </si>
   <si>
     <t>8.01A0.015200</t>
   </si>
   <si>
-    <t>EMG ELECTRODE 3 Pin</t>
-  </si>
-  <si>
     <t>1K</t>
   </si>
   <si>
@@ -129,21 +126,21 @@
     <t>J4</t>
   </si>
   <si>
-    <t>J16</t>
-  </si>
-  <si>
     <t>R1, R9, R24, R32, R37, R45, R50, R58, R63, R71, R76, R84, R89, R97, R102, R110</t>
   </si>
   <si>
     <t>R2, R7, R10, R12, R14, R15, R16, R18, R19, R20, R22, R23, R25, R30, R33, R35, R38, R43, R46, R48, R51, R56, R59, R61, R64, R69, R72, R74, R77, R82, R85, R87, R90, R95, R98, R100, R103, R108, R111, R113</t>
   </si>
   <si>
-    <t>R3, R4, R8, R26, R27, R31, R39, R40, R44, R52, R53, R57, R65, R66, R70, R78, R79, R83, R91, R92, R96, R104, R105, R109</t>
+    <t>R3, R4, R26, R27, R39, R40, R52, R53, R65, R66, R78, R79, R91, R92, R104, R105</t>
   </si>
   <si>
     <t>R5, R6, R11, R13, R17, R21, R28, R29, R34, R36, R41, R42, R47, R49, R54, R55, R60, R62, R67, R68, R73, R75, R80, R81, R86, R88, R93, R94, R99, R101, R106, R107, R112, R114</t>
   </si>
   <si>
+    <t>R8, R31, R44, R57, R70, R83, R96, R109</t>
+  </si>
+  <si>
     <t>R115, R116, R117, R118, R119, R120, R121</t>
   </si>
   <si>
@@ -177,10 +174,7 @@
     <t>SOD323F</t>
   </si>
   <si>
-    <t>EMG 2 PAD</t>
-  </si>
-  <si>
-    <t>EMG 3 Pad</t>
+    <t>SEMG-PAD</t>
   </si>
   <si>
     <t>Res-0603</t>
@@ -240,10 +234,13 @@
     <t>C106235</t>
   </si>
   <si>
+    <t>C138033</t>
+  </si>
+  <si>
+    <t>C60490</t>
+  </si>
+  <si>
     <t>C105578</t>
-  </si>
-  <si>
-    <t>C60490</t>
   </si>
   <si>
     <t>C95177</t>
@@ -721,13 +718,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -735,13 +732,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -749,13 +746,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -763,13 +760,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -777,13 +774,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -791,13 +788,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -805,13 +802,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -819,13 +816,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -833,13 +830,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -847,13 +844,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -861,13 +858,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -875,13 +872,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -889,165 +886,167 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="48" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="C19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="48" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
